--- a/6_redes_neuronales/1_red_neuronal_mlp/2_datos/1_raw/7_columnas_dataset_rezago_epi.xlsx
+++ b/6_redes_neuronales/1_red_neuronal_mlp/2_datos/1_raw/7_columnas_dataset_rezago_epi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documentos\investigacion\machine_learning_idalina\6_redes_neuronales\1_red_neuronal_1_sklearn_mlp\2_datos\1_raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documentos\investigacion\machine_learning_idalina\6_redes_neuronales\1_red_neuronal_mlp\2_datos\1_raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27622BAE-5FFB-4F55-AAD3-34709ED060FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F510C83B-7FEC-4BE9-9CED-DF922044226B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -412,6 +412,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="29.453125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -435,67 +438,67 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/6_redes_neuronales/1_red_neuronal_mlp/2_datos/1_raw/7_columnas_dataset_rezago_epi.xlsx
+++ b/6_redes_neuronales/1_red_neuronal_mlp/2_datos/1_raw/7_columnas_dataset_rezago_epi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documentos\investigacion\machine_learning_idalina\6_redes_neuronales\1_red_neuronal_mlp\2_datos\1_raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documentos\investigacion\machine_learning_idalina\3_xgboost\2_datos\1_raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F510C83B-7FEC-4BE9-9CED-DF922044226B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E80719-6639-4D80-A404-726A2799EA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>columnas</t>
   </si>
   <si>
     <t>fecha</t>
-  </si>
-  <si>
-    <t>año</t>
   </si>
   <si>
     <t>semana_epi</t>
@@ -410,11 +407,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="29.453125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -438,67 +432,62 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
